--- a/app/reports/LCU_research.xlsx
+++ b/app/reports/LCU_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-13 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-14 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>

--- a/app/reports/LCU_research.xlsx
+++ b/app/reports/LCU_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-14 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-15 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.05220999717712402</v>
+        <v>0.05085000038146972</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/LCU_research.xlsx
+++ b/app/reports/LCU_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-15 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-16 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.05085000038146972</v>
+        <v>0.05105999946594238</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/LCU_research.xlsx
+++ b/app/reports/LCU_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-16 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-17 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.05105999946594238</v>
+        <v>0.05098000049591064</v>
       </c>
     </row>
     <row r="6">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="B5" s="26" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>Lion Copper Corp. Common Shares</t>
         </is>
       </c>
       <c r="C5" s="27" t="n"/>

--- a/app/reports/LCU_research.xlsx
+++ b/app/reports/LCU_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-17 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-18 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>

--- a/app/reports/LCU_research.xlsx
+++ b/app/reports/LCU_research.xlsx
@@ -19,10 +19,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="6">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="166" formatCode="0.0000"/>
-    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="167" formatCode="0.0000"/>
     <numFmt numFmtId="168" formatCode="+0.0%;-0.0%"/>
     <numFmt numFmtId="169" formatCode="0.0"/>
   </numFmts>
@@ -111,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -122,30 +122,31 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -614,7 +615,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-18 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-19 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -684,10 +685,8 @@
           <t>Market price</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B9" s="6" t="n">
+        <v>4.501</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -850,8 +849,8 @@
           <t>Risk-free rate (10y Treasury)</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
-        <v>0.05098000049591064</v>
+      <c r="B5" s="7" t="n">
+        <v>0.0514799976348877</v>
       </c>
     </row>
     <row r="6">
@@ -860,7 +859,7 @@
           <t>Equity risk premium (ERP)</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="7" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -870,7 +869,7 @@
           <t>Beta (levered)</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -880,7 +879,7 @@
           <t>Credit spread over risk-free</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="7" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -890,7 +889,7 @@
           <t>Tax rate</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="7" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -900,7 +899,7 @@
           <t>Equity weight (cap structure)</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n">
+      <c r="B10" s="9" t="n">
         <v>0.7</v>
       </c>
     </row>
@@ -910,7 +909,7 @@
           <t>FCF growth (flat, faded avg)</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="7" t="n">
         <v>0.0125</v>
       </c>
     </row>
@@ -920,7 +919,7 @@
           <t>Terminal growth rate</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="7" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -930,7 +929,7 @@
           <t>Latest FCF ($, base year)</t>
         </is>
       </c>
-      <c r="B13" s="9" t="n">
+      <c r="B13" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -940,7 +939,7 @@
           <t>Cost of equity (CAPM)</t>
         </is>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="11">
         <f>B5+B7*B6</f>
         <v/>
       </c>
@@ -951,18 +950,18 @@
           <t>After-tax cost of debt</t>
         </is>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="11">
         <f>(B5+B8)*(1-B9)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>WACC</t>
         </is>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="13">
         <f>B10*B15+(1-B10)*B16</f>
         <v/>
       </c>
@@ -1009,23 +1008,23 @@
           <t>Projected FCF</t>
         </is>
       </c>
-      <c r="B22" s="13">
+      <c r="B22" s="14">
         <f>$B$13*(1+$B$11)</f>
         <v/>
       </c>
-      <c r="C22" s="13">
+      <c r="C22" s="14">
         <f>B22*(1+$B$11)</f>
         <v/>
       </c>
-      <c r="D22" s="13">
+      <c r="D22" s="14">
         <f>C22*(1+$B$11)</f>
         <v/>
       </c>
-      <c r="E22" s="13">
+      <c r="E22" s="14">
         <f>D22*(1+$B$11)</f>
         <v/>
       </c>
-      <c r="F22" s="13">
+      <c r="F22" s="14">
         <f>E22*(1+$B$11)</f>
         <v/>
       </c>
@@ -1036,23 +1035,23 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B23" s="14">
+      <c r="B23" s="15">
         <f>1/(1+$B$17)^1</f>
         <v/>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="15">
         <f>1/(1+$B$17)^2</f>
         <v/>
       </c>
-      <c r="D23" s="14">
+      <c r="D23" s="15">
         <f>1/(1+$B$17)^3</f>
         <v/>
       </c>
-      <c r="E23" s="14">
+      <c r="E23" s="15">
         <f>1/(1+$B$17)^4</f>
         <v/>
       </c>
-      <c r="F23" s="14">
+      <c r="F23" s="15">
         <f>1/(1+$B$17)^5</f>
         <v/>
       </c>
@@ -1063,23 +1062,23 @@
           <t>PV of FCF</t>
         </is>
       </c>
-      <c r="B24" s="13">
+      <c r="B24" s="14">
         <f>B22*B23</f>
         <v/>
       </c>
-      <c r="C24" s="13">
+      <c r="C24" s="14">
         <f>C22*C23</f>
         <v/>
       </c>
-      <c r="D24" s="13">
+      <c r="D24" s="14">
         <f>D22*D23</f>
         <v/>
       </c>
-      <c r="E24" s="13">
+      <c r="E24" s="14">
         <f>E22*E23</f>
         <v/>
       </c>
-      <c r="F24" s="13">
+      <c r="F24" s="14">
         <f>F22*F23</f>
         <v/>
       </c>
@@ -1090,7 +1089,7 @@
           <t>Sum of PV (explicit 5y)</t>
         </is>
       </c>
-      <c r="B26" s="13">
+      <c r="B26" s="14">
         <f>SUM(B24:F24)</f>
         <v/>
       </c>
@@ -1101,7 +1100,7 @@
           <t>Terminal value (Gordon)</t>
         </is>
       </c>
-      <c r="B27" s="13">
+      <c r="B27" s="14">
         <f>F22*(1+B12)/(B17-B12)</f>
         <v/>
       </c>
@@ -1112,18 +1111,18 @@
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="B28" s="13">
+      <c r="B28" s="14">
         <f>B27/(1+B17)^5</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="B29" s="16">
+      <c r="B29" s="17">
         <f>B26+B28</f>
         <v/>
       </c>
@@ -1148,7 +1147,7 @@
           <t>Less: total debt</t>
         </is>
       </c>
-      <c r="B32" s="9" t="n">
+      <c r="B32" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1158,7 +1157,7 @@
           <t>Plus: cash &amp; ST investments</t>
         </is>
       </c>
-      <c r="B33" s="9" t="n">
+      <c r="B33" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1168,7 +1167,7 @@
           <t>Equity value</t>
         </is>
       </c>
-      <c r="B34" s="13">
+      <c r="B34" s="14">
         <f>B29-B32+B33</f>
         <v/>
       </c>
@@ -1179,17 +1178,17 @@
           <t>Diluted shares outstanding</t>
         </is>
       </c>
-      <c r="B35" s="17" t="n">
-        <v>0</v>
+      <c r="B35" s="18" t="n">
+        <v>15975262.38613641</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>Intrinsic per share</t>
         </is>
       </c>
-      <c r="B36" s="18">
+      <c r="B36" s="19">
         <f>B34/B35</f>
         <v/>
       </c>
@@ -1200,17 +1199,17 @@
           <t>Current market price</t>
         </is>
       </c>
-      <c r="B37" s="19" t="n">
-        <v>0</v>
+      <c r="B37" s="20" t="n">
+        <v>4.501</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>Margin of safety</t>
         </is>
       </c>
-      <c r="B38" s="20">
+      <c r="B38" s="21">
         <f>(B36-B37)/B37</f>
         <v/>
       </c>
@@ -1230,158 +1229,158 @@
       <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="21" t="inlineStr">
+      <c r="A42" s="22" t="inlineStr">
         <is>
           <t>WACC ↓ / TermG →</t>
         </is>
       </c>
-      <c r="B42" s="22">
+      <c r="B42" s="23">
         <f>$B$12+-0.01</f>
         <v/>
       </c>
-      <c r="C42" s="22">
+      <c r="C42" s="23">
         <f>$B$12+-0.005</f>
         <v/>
       </c>
-      <c r="D42" s="22">
+      <c r="D42" s="23">
         <f>$B$12+0.0</f>
         <v/>
       </c>
-      <c r="E42" s="22">
+      <c r="E42" s="23">
         <f>$B$12+0.005</f>
         <v/>
       </c>
-      <c r="F42" s="22">
+      <c r="F42" s="23">
         <f>$B$12+0.01</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="22">
+      <c r="A43" s="23">
         <f>$B$17+-0.01</f>
         <v/>
       </c>
-      <c r="B43" s="23">
+      <c r="B43" s="24">
         <f>($B$13*(1+$B$11)^1/(1+A43)^1+$B$13*(1+$B$11)^2/(1+A43)^2+$B$13*(1+$B$11)^3/(1+A43)^3+$B$13*(1+$B$11)^4/(1+A43)^4+$B$13*(1+$B$11)^5/(1+A43)^5+($B$13*(1+$B$11)^5*(1+B$42)/(A43-B$42))/(1+A43)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="C43" s="23">
+      <c r="C43" s="24">
         <f>($B$13*(1+$B$11)^1/(1+A43)^1+$B$13*(1+$B$11)^2/(1+A43)^2+$B$13*(1+$B$11)^3/(1+A43)^3+$B$13*(1+$B$11)^4/(1+A43)^4+$B$13*(1+$B$11)^5/(1+A43)^5+($B$13*(1+$B$11)^5*(1+C$42)/(A43-C$42))/(1+A43)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="D43" s="23">
+      <c r="D43" s="24">
         <f>($B$13*(1+$B$11)^1/(1+A43)^1+$B$13*(1+$B$11)^2/(1+A43)^2+$B$13*(1+$B$11)^3/(1+A43)^3+$B$13*(1+$B$11)^4/(1+A43)^4+$B$13*(1+$B$11)^5/(1+A43)^5+($B$13*(1+$B$11)^5*(1+D$42)/(A43-D$42))/(1+A43)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="E43" s="23">
+      <c r="E43" s="24">
         <f>($B$13*(1+$B$11)^1/(1+A43)^1+$B$13*(1+$B$11)^2/(1+A43)^2+$B$13*(1+$B$11)^3/(1+A43)^3+$B$13*(1+$B$11)^4/(1+A43)^4+$B$13*(1+$B$11)^5/(1+A43)^5+($B$13*(1+$B$11)^5*(1+E$42)/(A43-E$42))/(1+A43)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="F43" s="23">
+      <c r="F43" s="24">
         <f>($B$13*(1+$B$11)^1/(1+A43)^1+$B$13*(1+$B$11)^2/(1+A43)^2+$B$13*(1+$B$11)^3/(1+A43)^3+$B$13*(1+$B$11)^4/(1+A43)^4+$B$13*(1+$B$11)^5/(1+A43)^5+($B$13*(1+$B$11)^5*(1+F$42)/(A43-F$42))/(1+A43)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="22">
+      <c r="A44" s="23">
         <f>$B$17+-0.005</f>
         <v/>
       </c>
-      <c r="B44" s="23">
+      <c r="B44" s="24">
         <f>($B$13*(1+$B$11)^1/(1+A44)^1+$B$13*(1+$B$11)^2/(1+A44)^2+$B$13*(1+$B$11)^3/(1+A44)^3+$B$13*(1+$B$11)^4/(1+A44)^4+$B$13*(1+$B$11)^5/(1+A44)^5+($B$13*(1+$B$11)^5*(1+B$42)/(A44-B$42))/(1+A44)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="C44" s="23">
+      <c r="C44" s="24">
         <f>($B$13*(1+$B$11)^1/(1+A44)^1+$B$13*(1+$B$11)^2/(1+A44)^2+$B$13*(1+$B$11)^3/(1+A44)^3+$B$13*(1+$B$11)^4/(1+A44)^4+$B$13*(1+$B$11)^5/(1+A44)^5+($B$13*(1+$B$11)^5*(1+C$42)/(A44-C$42))/(1+A44)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="D44" s="23">
+      <c r="D44" s="24">
         <f>($B$13*(1+$B$11)^1/(1+A44)^1+$B$13*(1+$B$11)^2/(1+A44)^2+$B$13*(1+$B$11)^3/(1+A44)^3+$B$13*(1+$B$11)^4/(1+A44)^4+$B$13*(1+$B$11)^5/(1+A44)^5+($B$13*(1+$B$11)^5*(1+D$42)/(A44-D$42))/(1+A44)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="E44" s="23">
+      <c r="E44" s="24">
         <f>($B$13*(1+$B$11)^1/(1+A44)^1+$B$13*(1+$B$11)^2/(1+A44)^2+$B$13*(1+$B$11)^3/(1+A44)^3+$B$13*(1+$B$11)^4/(1+A44)^4+$B$13*(1+$B$11)^5/(1+A44)^5+($B$13*(1+$B$11)^5*(1+E$42)/(A44-E$42))/(1+A44)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="F44" s="23">
+      <c r="F44" s="24">
         <f>($B$13*(1+$B$11)^1/(1+A44)^1+$B$13*(1+$B$11)^2/(1+A44)^2+$B$13*(1+$B$11)^3/(1+A44)^3+$B$13*(1+$B$11)^4/(1+A44)^4+$B$13*(1+$B$11)^5/(1+A44)^5+($B$13*(1+$B$11)^5*(1+F$42)/(A44-F$42))/(1+A44)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="22">
+      <c r="A45" s="23">
         <f>$B$17+0.0</f>
         <v/>
       </c>
-      <c r="B45" s="23">
+      <c r="B45" s="24">
         <f>($B$13*(1+$B$11)^1/(1+A45)^1+$B$13*(1+$B$11)^2/(1+A45)^2+$B$13*(1+$B$11)^3/(1+A45)^3+$B$13*(1+$B$11)^4/(1+A45)^4+$B$13*(1+$B$11)^5/(1+A45)^5+($B$13*(1+$B$11)^5*(1+B$42)/(A45-B$42))/(1+A45)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="C45" s="23">
+      <c r="C45" s="24">
         <f>($B$13*(1+$B$11)^1/(1+A45)^1+$B$13*(1+$B$11)^2/(1+A45)^2+$B$13*(1+$B$11)^3/(1+A45)^3+$B$13*(1+$B$11)^4/(1+A45)^4+$B$13*(1+$B$11)^5/(1+A45)^5+($B$13*(1+$B$11)^5*(1+C$42)/(A45-C$42))/(1+A45)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="D45" s="24">
+      <c r="D45" s="25">
         <f>($B$13*(1+$B$11)^1/(1+A45)^1+$B$13*(1+$B$11)^2/(1+A45)^2+$B$13*(1+$B$11)^3/(1+A45)^3+$B$13*(1+$B$11)^4/(1+A45)^4+$B$13*(1+$B$11)^5/(1+A45)^5+($B$13*(1+$B$11)^5*(1+D$42)/(A45-D$42))/(1+A45)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="E45" s="23">
+      <c r="E45" s="24">
         <f>($B$13*(1+$B$11)^1/(1+A45)^1+$B$13*(1+$B$11)^2/(1+A45)^2+$B$13*(1+$B$11)^3/(1+A45)^3+$B$13*(1+$B$11)^4/(1+A45)^4+$B$13*(1+$B$11)^5/(1+A45)^5+($B$13*(1+$B$11)^5*(1+E$42)/(A45-E$42))/(1+A45)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="F45" s="23">
+      <c r="F45" s="24">
         <f>($B$13*(1+$B$11)^1/(1+A45)^1+$B$13*(1+$B$11)^2/(1+A45)^2+$B$13*(1+$B$11)^3/(1+A45)^3+$B$13*(1+$B$11)^4/(1+A45)^4+$B$13*(1+$B$11)^5/(1+A45)^5+($B$13*(1+$B$11)^5*(1+F$42)/(A45-F$42))/(1+A45)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="22">
+      <c r="A46" s="23">
         <f>$B$17+0.005</f>
         <v/>
       </c>
-      <c r="B46" s="23">
+      <c r="B46" s="24">
         <f>($B$13*(1+$B$11)^1/(1+A46)^1+$B$13*(1+$B$11)^2/(1+A46)^2+$B$13*(1+$B$11)^3/(1+A46)^3+$B$13*(1+$B$11)^4/(1+A46)^4+$B$13*(1+$B$11)^5/(1+A46)^5+($B$13*(1+$B$11)^5*(1+B$42)/(A46-B$42))/(1+A46)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="C46" s="23">
+      <c r="C46" s="24">
         <f>($B$13*(1+$B$11)^1/(1+A46)^1+$B$13*(1+$B$11)^2/(1+A46)^2+$B$13*(1+$B$11)^3/(1+A46)^3+$B$13*(1+$B$11)^4/(1+A46)^4+$B$13*(1+$B$11)^5/(1+A46)^5+($B$13*(1+$B$11)^5*(1+C$42)/(A46-C$42))/(1+A46)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="D46" s="23">
+      <c r="D46" s="24">
         <f>($B$13*(1+$B$11)^1/(1+A46)^1+$B$13*(1+$B$11)^2/(1+A46)^2+$B$13*(1+$B$11)^3/(1+A46)^3+$B$13*(1+$B$11)^4/(1+A46)^4+$B$13*(1+$B$11)^5/(1+A46)^5+($B$13*(1+$B$11)^5*(1+D$42)/(A46-D$42))/(1+A46)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="E46" s="23">
+      <c r="E46" s="24">
         <f>($B$13*(1+$B$11)^1/(1+A46)^1+$B$13*(1+$B$11)^2/(1+A46)^2+$B$13*(1+$B$11)^3/(1+A46)^3+$B$13*(1+$B$11)^4/(1+A46)^4+$B$13*(1+$B$11)^5/(1+A46)^5+($B$13*(1+$B$11)^5*(1+E$42)/(A46-E$42))/(1+A46)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="F46" s="23">
+      <c r="F46" s="24">
         <f>($B$13*(1+$B$11)^1/(1+A46)^1+$B$13*(1+$B$11)^2/(1+A46)^2+$B$13*(1+$B$11)^3/(1+A46)^3+$B$13*(1+$B$11)^4/(1+A46)^4+$B$13*(1+$B$11)^5/(1+A46)^5+($B$13*(1+$B$11)^5*(1+F$42)/(A46-F$42))/(1+A46)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="22">
+      <c r="A47" s="23">
         <f>$B$17+0.01</f>
         <v/>
       </c>
-      <c r="B47" s="23">
+      <c r="B47" s="24">
         <f>($B$13*(1+$B$11)^1/(1+A47)^1+$B$13*(1+$B$11)^2/(1+A47)^2+$B$13*(1+$B$11)^3/(1+A47)^3+$B$13*(1+$B$11)^4/(1+A47)^4+$B$13*(1+$B$11)^5/(1+A47)^5+($B$13*(1+$B$11)^5*(1+B$42)/(A47-B$42))/(1+A47)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="C47" s="23">
+      <c r="C47" s="24">
         <f>($B$13*(1+$B$11)^1/(1+A47)^1+$B$13*(1+$B$11)^2/(1+A47)^2+$B$13*(1+$B$11)^3/(1+A47)^3+$B$13*(1+$B$11)^4/(1+A47)^4+$B$13*(1+$B$11)^5/(1+A47)^5+($B$13*(1+$B$11)^5*(1+C$42)/(A47-C$42))/(1+A47)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="D47" s="23">
+      <c r="D47" s="24">
         <f>($B$13*(1+$B$11)^1/(1+A47)^1+$B$13*(1+$B$11)^2/(1+A47)^2+$B$13*(1+$B$11)^3/(1+A47)^3+$B$13*(1+$B$11)^4/(1+A47)^4+$B$13*(1+$B$11)^5/(1+A47)^5+($B$13*(1+$B$11)^5*(1+D$42)/(A47-D$42))/(1+A47)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="E47" s="23">
+      <c r="E47" s="24">
         <f>($B$13*(1+$B$11)^1/(1+A47)^1+$B$13*(1+$B$11)^2/(1+A47)^2+$B$13*(1+$B$11)^3/(1+A47)^3+$B$13*(1+$B$11)^4/(1+A47)^4+$B$13*(1+$B$11)^5/(1+A47)^5+($B$13*(1+$B$11)^5*(1+E$42)/(A47-E$42))/(1+A47)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="F47" s="23">
+      <c r="F47" s="24">
         <f>($B$13*(1+$B$11)^1/(1+A47)^1+$B$13*(1+$B$11)^2/(1+A47)^2+$B$13*(1+$B$11)^3/(1+A47)^3+$B$13*(1+$B$11)^4/(1+A47)^4+$B$13*(1+$B$11)^5/(1+A47)^5+($B$13*(1+$B$11)^5*(1+F$42)/(A47-F$42))/(1+A47)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
@@ -1437,52 +1436,54 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="25" t="inlineStr">
+      <c r="A4" s="26" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="26" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="26" t="inlineStr">
         <is>
           <t>Market Cap</t>
         </is>
       </c>
-      <c r="D4" s="25" t="inlineStr">
+      <c r="D4" s="26" t="inlineStr">
         <is>
           <t>P/E (TTM)</t>
         </is>
       </c>
-      <c r="E4" s="25" t="inlineStr">
+      <c r="E4" s="26" t="inlineStr">
         <is>
           <t>EV/EBITDA</t>
         </is>
       </c>
-      <c r="F4" s="25" t="inlineStr">
+      <c r="F4" s="26" t="inlineStr">
         <is>
           <t>EV/Revenue</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>LCU</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>Lion Copper Corp. Common Shares</t>
         </is>
       </c>
-      <c r="C5" s="27" t="n"/>
-      <c r="D5" s="28" t="n"/>
-      <c r="E5" s="28" t="n"/>
-      <c r="F5" s="28" t="n"/>
+      <c r="C5" s="28" t="n">
+        <v>71904656</v>
+      </c>
+      <c r="D5" s="29" t="n"/>
+      <c r="E5" s="29" t="n"/>
+      <c r="F5" s="29" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1490,15 +1491,15 @@
           <t>Peer median</t>
         </is>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <f>MEDIAN(D6:D5)</f>
         <v/>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <f>MEDIAN(E6:E5)</f>
         <v/>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <f>MEDIAN(F6:F5)</f>
         <v/>
       </c>
@@ -1509,15 +1510,15 @@
           <t>Peer mean</t>
         </is>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <f>AVERAGE(D6:D5)</f>
         <v/>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <f>AVERAGE(E6:E5)</f>
         <v/>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="30">
         <f>AVERAGE(F6:F5)</f>
         <v/>
       </c>
@@ -1528,9 +1529,9 @@
           <t>Target percentile vs peers</t>
         </is>
       </c>
-      <c r="D9" s="30" t="n"/>
-      <c r="E9" s="30" t="n"/>
-      <c r="F9" s="30" t="n"/>
+      <c r="D9" s="31" t="n"/>
+      <c r="E9" s="31" t="n"/>
+      <c r="F9" s="31" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
